--- a/Project_ETF/ETF_Investment_Portfolio/00713/ETF_Investment_Portfolio_20260831.xlsx
+++ b/Project_ETF/ETF_Investment_Portfolio/00713/ETF_Investment_Portfolio_20260831.xlsx
@@ -1151,17 +1151,17 @@
     <row r="46">
       <c r="A46" s="3" t="inlineStr">
         <is>
-          <t>2207</t>
+          <t>2618</t>
         </is>
       </c>
       <c r="B46" s="3" t="inlineStr">
         <is>
-          <t>和泰車</t>
+          <t>長榮航</t>
         </is>
       </c>
       <c r="C46" s="4" t="inlineStr">
         <is>
-          <t>2,330,000</t>
+          <t>28,657,000</t>
         </is>
       </c>
       <c r="D46" s="4" t="inlineStr">
@@ -1173,17 +1173,17 @@
     <row r="47">
       <c r="A47" s="3" t="inlineStr">
         <is>
-          <t>2618</t>
+          <t>2207</t>
         </is>
       </c>
       <c r="B47" s="3" t="inlineStr">
         <is>
-          <t>長榮航</t>
+          <t>和泰車</t>
         </is>
       </c>
       <c r="C47" s="4" t="inlineStr">
         <is>
-          <t>28,657,000</t>
+          <t>2,330,000</t>
         </is>
       </c>
       <c r="D47" s="4" t="inlineStr">
@@ -1305,17 +1305,17 @@
     <row r="53">
       <c r="A53" s="3" t="inlineStr">
         <is>
-          <t>2347</t>
+          <t>6670</t>
         </is>
       </c>
       <c r="B53" s="3" t="inlineStr">
         <is>
-          <t>聯強</t>
+          <t>復盛應用</t>
         </is>
       </c>
       <c r="C53" s="4" t="inlineStr">
         <is>
-          <t>12,795,000</t>
+          <t>3,863,000</t>
         </is>
       </c>
       <c r="D53" s="4" t="inlineStr">
@@ -1327,17 +1327,17 @@
     <row r="54">
       <c r="A54" s="3" t="inlineStr">
         <is>
-          <t>6670</t>
+          <t>2347</t>
         </is>
       </c>
       <c r="B54" s="3" t="inlineStr">
         <is>
-          <t>復盛應用</t>
+          <t>聯強</t>
         </is>
       </c>
       <c r="C54" s="4" t="inlineStr">
         <is>
-          <t>3,863,000</t>
+          <t>12,795,000</t>
         </is>
       </c>
       <c r="D54" s="4" t="inlineStr">
